--- a/Tracker.xlsx
+++ b/Tracker.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://durvahconsulting-my.sharepoint.com/personal/srk_durvah_com/Documents/From G Suite Drive/USME/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{046BB8D6-BFAC-4F83-AD1C-E30EBFD421E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{577B82F6-B36F-4847-B237-473CE4C321FC}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="8_{046BB8D6-BFAC-4F83-AD1C-E30EBFD421E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FB6C8BB-A932-4792-809B-6952FAEC19F8}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{E54EACC6-DD53-479E-AB22-921572843852}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="48">
   <si>
     <t>Sl</t>
   </si>
@@ -160,6 +161,33 @@
   </si>
   <si>
     <t>Opportunity Forecast</t>
+  </si>
+  <si>
+    <t>Trade Agreements</t>
+  </si>
+  <si>
+    <t>Quote</t>
+  </si>
+  <si>
+    <t>working on solution</t>
+  </si>
+  <si>
+    <t>Group Agreement</t>
+  </si>
+  <si>
+    <t>Account</t>
+  </si>
+  <si>
+    <t>&lt;&gt;</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>GPO</t>
   </si>
 </sst>
 </file>
@@ -797,8 +825,8 @@
         <v>5</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="4" t="s">
-        <v>22</v>
+      <c r="E17" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -937,7 +965,9 @@
         <v>5</v>
       </c>
       <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
+      <c r="E29" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.45">
@@ -1002,8 +1032,8 @@
         <v>5</v>
       </c>
       <c r="D35" s="2"/>
-      <c r="E35" s="4" t="s">
-        <v>22</v>
+      <c r="E35" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>28</v>
@@ -1060,8 +1090,8 @@
         <v>14</v>
       </c>
       <c r="D40" s="2"/>
-      <c r="E40" s="4" t="s">
-        <v>22</v>
+      <c r="E40" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>33</v>
@@ -1074,7 +1104,9 @@
         <v>5</v>
       </c>
       <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
+      <c r="E41" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="F41" s="2"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.45">
@@ -1274,8 +1306,12 @@
         <v>5</v>
       </c>
       <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
+      <c r="E59" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A60" s="2"/>
@@ -1582,4 +1618,59 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1F6F111-4D01-4AE0-BD2E-1E01F5F4A70B}">
+  <dimension ref="H8:P17"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="14" max="14" width="16.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="8" spans="8:16" x14ac:dyDescent="0.45">
+      <c r="P8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="8:16" x14ac:dyDescent="0.45">
+      <c r="I10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="8:16" x14ac:dyDescent="0.45">
+      <c r="J11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="8:16" x14ac:dyDescent="0.45">
+      <c r="H15" t="s">
+        <v>43</v>
+      </c>
+      <c r="M15" t="s">
+        <v>44</v>
+      </c>
+      <c r="N15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="8:16" x14ac:dyDescent="0.45">
+      <c r="H16" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.45">
+      <c r="H17" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>